--- a/faq/sms.xlsx
+++ b/faq/sms.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,214 +450,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  'При смене SIM-карты без изменения номера СМС-сообщения будут приходить без изменений.'</t>
+          <t xml:space="preserve">  '«3D Secure» — технология, предназначенная для обеспечения безопасности интернет-платежей, совершенных с использованием карт международных платежных систем «MASTERCARD», «VISA.», «Union Pay International».'</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>При смене SIM-карты без изменения номера СМС-сообщения будут приходить без изменений.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Если льготный период не кончился, то при повторном подключении услуги «Сервис уведомлений» дата начала периода переходит с прошлого подключения.'</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Если льготный период не кончился, то при повторном подключении услуги «Сервис уведомлений» дата начала периода переходит с прошлого подключения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'При повторном подключении уведомлений после окончания льготного периода будет взиматься комиссия.'</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>При повторном подключении уведомлений после окончания льготного периода будет взиматься комиссия.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Услуга «Сервис уведомлений» отключается автоматически в случаях:</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Услуга «Сервис уведомлений» отключается автоматически в случаях:</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Блокировки и изменения активного статуса карты</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>• Блокировки и изменения активного статуса карты</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Окончания срока действия карты (если не был осуществлен её перевыпуск на очередной срок)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>• Окончания срока действия карты (если не был осуществлен её перевыпуск на очередной срок)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Закрытия карты</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>• Закрытия карты</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • При недостаточности денежных средств на счете или неиспользованном лимите кредитования (по кредитным картам и договорам с овердрафтом) в размере, необходимом для списания комиссии согласно тарифному плану</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>• При недостаточности денежных средств на счете или неиспользованном лимите кредитования (по кредитным картам и договорам с овердрафтом) в размере, необходимом для списания комиссии согласно тарифному плану</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Если вы пользуетесь мобильным приложением, то направляются всплывающие уведомления.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Если вы пользуетесь мобильным приложением, то направляются всплывающие уведомления.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>whatIsPush: Всплывающие уведомления — это текстовое сообщение, направляемое банком клиенту с помощью интернета на мобильное устройство, к номеру которого подключена услуга «Сервис уведомлений».</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Всплывающие уведомления — это текстовое сообщение, направляемое банком клиенту с помощью интернета на мобильное устройство, к номеру которого подключена услуга «Сервис уведомлений».</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Всплывающие уведомления отключаются автоматически:</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Всплывающие уведомления отключаются автоматически:</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Если отключается услуга «Сервис уведомлений»</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>• Если отключается услуга «Сервис уведомлений»</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Если вы самостоятельно отключили всплывающие уведомления в настройках смартфона или приложения «Уралсиб Онлайн»</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>• Если вы самостоятельно отключили всплывающие уведомления в настройках смартфона или приложения «Уралсиб Онлайн»</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>26</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  '«3D Secure» — технология, предназначенная для обеспечения безопасности интернет-платежей, совершенных с использованием карт международных платежных систем «MASTERCARD», «VISA.», «Union Pay International».'</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>«3D Secure» — технология, предназначенная для обеспечения безопасности интернет-платежей, совершенных с использованием карт международных платежных систем «MASTERCARD», «VISA», «Union Pay International».</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t xml:space="preserve">  '«3D Secure» — технология, предназначенная для обеспечения безопасности интернет-платежей, совершенных с использованием карт международных платежных систем «MASTERCARD», «VISA», «Union Pay International».'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>убрана лишняя точка внутри кавычек «VISA.»</t>
         </is>
